--- a/reports/tables/FirstVisit_TestSet_Bootstrap_CI.xlsx
+++ b/reports/tables/FirstVisit_TestSet_Bootstrap_CI.xlsx
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5901912616248465</v>
+        <v>0.6473065450078961</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4914915544730513</v>
+        <v>0.5703665428691177</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6758094655110046</v>
+        <v>0.7206272962771606</v>
       </c>
     </row>
     <row r="3">
@@ -473,13 +473,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.09237231090921177</v>
+        <v>0.1045898395339543</v>
       </c>
       <c r="C3" t="n">
-        <v>0.06211961040008362</v>
+        <v>0.06934921368406347</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1598209339754835</v>
+        <v>0.1832116175106888</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +489,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.07023954615998154</v>
+        <v>0.06442108805891836</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05324155181379558</v>
+        <v>0.04824872626502071</v>
       </c>
       <c r="D4" t="n">
-        <v>0.08787358697959678</v>
+        <v>0.08093479232608981</v>
       </c>
     </row>
     <row r="5">
@@ -505,13 +505,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4878048780487805</v>
+        <v>0.5853658536585366</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3414634146341464</v>
+        <v>0.4249519230769231</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6429315476190476</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="6">
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6780575539568345</v>
+        <v>0.6133093525179856</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6238926613063613</v>
+        <v>0.5634702517162471</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7276111568950632</v>
+        <v>0.6655133518002055</v>
       </c>
     </row>
     <row r="7">
@@ -537,13 +537,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9472361809045227</v>
+        <v>0.9525139664804469</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9255563740694789</v>
+        <v>0.9283744583106397</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9672202868852459</v>
+        <v>0.9741488895382817</v>
       </c>
     </row>
     <row r="8">
@@ -553,13 +553,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1005025125628141</v>
+        <v>0.100418410041841</v>
       </c>
       <c r="C8" t="n">
-        <v>0.06060253699788583</v>
+        <v>0.06437466604615888</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1449312908312683</v>
+        <v>0.1407800088261253</v>
       </c>
     </row>
   </sheetData>
